--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_JERSEY_2012.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2012/NEW_JERSEY_2012.xlsx
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C101">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C590">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C646">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C647">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C652">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B1014" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1014">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="B1048" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1048">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1152">
